--- a/data/hex_xlsx/BOREO.HE.xlsx
+++ b/data/hex_xlsx/BOREO.HE.xlsx
@@ -699,7 +699,7 @@
     <t>Total Assets</t>
   </si>
   <si>
-    <t>Financial Liabilities</t>
+    <t>Financial Liabilities ST</t>
   </si>
   <si>
     <t>Current portion of Capital Leases</t>
@@ -1391,7 +1391,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1469,6 +1469,12 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -9950,7 +9956,9 @@
         <f t="shared" si="1"/>
         <v>18.17</v>
       </c>
-      <c r="V49" s="17"/>
+      <c r="V49" s="17">
+        <v>20.07</v>
+      </c>
       <c r="W49" s="17">
         <f>SUM(W61:W63,W71)</f>
         <v>19.74</v>
@@ -11043,20 +11051,20 @@
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="26" t="s">
         <v>226</v>
       </c>
       <c r="B78" s="15">
         <v>119.32</v>
       </c>
       <c r="C78" s="17">
-        <v>87.08</v>
-      </c>
-      <c r="D78" s="15">
-        <v>106.26</v>
-      </c>
-      <c r="E78" s="15">
-        <v>104.84</v>
+        <v>57.66</v>
+      </c>
+      <c r="D78" s="17">
+        <v>81.65</v>
+      </c>
+      <c r="E78" s="17">
+        <v>83.87</v>
       </c>
       <c r="F78" s="17">
         <v>94.11</v>
@@ -11106,7 +11114,9 @@
       <c r="U78" s="17">
         <v>1.51</v>
       </c>
-      <c r="V78" s="16"/>
+      <c r="V78" s="27">
+        <v>0.0</v>
+      </c>
       <c r="W78" s="17">
         <v>0.2</v>
       </c>
@@ -17126,16 +17136,16 @@
       <c r="C51" s="23">
         <v>-55.77</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="28">
         <v>-122.06</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="28">
         <v>-131.22</v>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="28">
         <v>-120.92</v>
       </c>
-      <c r="G51" s="26">
+      <c r="G51" s="28">
         <v>-238.06</v>
       </c>
       <c r="H51" s="23">
@@ -19411,10 +19421,10 @@
       <c r="AA11" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="AB11" s="27" t="s">
+      <c r="AB11" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="AC11" s="28"/>
+      <c r="AC11" s="30"/>
       <c r="AD11" s="7" t="s">
         <v>347</v>
       </c>
@@ -19996,3582 +20006,3582 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="31" t="s">
         <v>357</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="33" t="s">
         <v>357</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="34">
         <v>735.2</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="34">
         <v>1297.79</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="34">
         <v>1377.16</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="34">
         <v>1966.48</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="34">
         <v>1007.15</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="34">
         <v>237.15</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="34">
         <v>158.56</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="34">
         <v>197.98</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="34">
         <v>103.83</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="34">
         <v>111.45</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="35">
         <v>59.26</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="35">
         <v>60.19</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="35">
         <v>83.62</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="35">
         <v>89.38</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="35">
         <v>45.88</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="35">
         <v>41.6</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="35">
         <v>45.24</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="35">
         <v>62.9</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="35">
         <v>53.76</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="35">
         <v>45.29</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="35">
         <v>64.49</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="35">
         <v>58.47</v>
       </c>
-      <c r="X21" s="33">
+      <c r="X21" s="35">
         <v>40.35</v>
       </c>
-      <c r="Y21" s="33">
+      <c r="Y21" s="35">
         <v>68.07</v>
       </c>
-      <c r="Z21" s="33">
+      <c r="Z21" s="35">
         <v>51.71</v>
       </c>
-      <c r="AA21" s="33">
+      <c r="AA21" s="35">
         <v>14.2</v>
       </c>
-      <c r="AB21" s="33">
+      <c r="AB21" s="35">
         <v>21.66</v>
       </c>
-      <c r="AC21" s="33">
+      <c r="AC21" s="35">
         <v>33.4</v>
       </c>
-      <c r="AD21" s="33">
+      <c r="AD21" s="35">
         <v>22.85</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="33" t="s">
         <v>358</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="34">
         <v>1417.74</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="34">
         <v>1261.77</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="34">
         <v>972.98</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="34">
         <v>706.35</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="34">
         <v>351.55</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="34">
         <v>163.86</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="34">
         <v>130.21</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="34">
         <v>112.09</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="35">
         <v>87.56</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="35">
         <v>92.8</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="35">
         <v>77.03</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="35">
         <v>68.49</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="35">
         <v>56.54</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="35">
         <v>54.24</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="35">
         <v>46.78</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="35">
         <v>49.46</v>
       </c>
-      <c r="R22" s="33">
+      <c r="R22" s="35">
         <v>63.36</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="35">
         <v>55.4</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="35">
         <v>53.55</v>
       </c>
-      <c r="U22" s="33">
+      <c r="U22" s="35">
         <v>55.19</v>
       </c>
-      <c r="V22" s="33">
+      <c r="V22" s="35">
         <v>57.91</v>
       </c>
-      <c r="W22" s="33">
+      <c r="W22" s="35">
         <v>48.82</v>
       </c>
-      <c r="X22" s="33">
+      <c r="X22" s="35">
         <v>35.68</v>
       </c>
-      <c r="Y22" s="33">
+      <c r="Y22" s="35">
         <v>36.73</v>
       </c>
-      <c r="Z22" s="33">
+      <c r="Z22" s="35">
         <v>28.87</v>
       </c>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="34"/>
-      <c r="AD22" s="34"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="31" t="s">
         <v>359</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="33" t="s">
         <v>359</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="34">
         <v>348.06</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="34">
         <v>867.16</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="34">
         <v>1038.52</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="34">
         <v>1545.99</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="34">
         <v>789.25</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="34">
         <v>267.3</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="34">
         <v>186.6</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="34">
         <v>216.96</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="34">
         <v>143.35</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="34">
         <v>143.7</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="35">
         <v>91.59</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="35">
         <v>83.21</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="35">
         <v>94.66</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="34">
         <v>113.01</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="35">
         <v>66.6</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="35">
         <v>59.42</v>
       </c>
-      <c r="R24" s="33">
+      <c r="R24" s="35">
         <v>62.7</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="35">
         <v>76.01</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="35">
         <v>66.2</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="35">
         <v>59.49</v>
       </c>
-      <c r="V24" s="33">
+      <c r="V24" s="35">
         <v>66.11</v>
       </c>
-      <c r="W24" s="33">
+      <c r="W24" s="35">
         <v>75.55</v>
       </c>
-      <c r="X24" s="33">
+      <c r="X24" s="35">
         <v>51.81</v>
       </c>
-      <c r="Y24" s="33">
+      <c r="Y24" s="35">
         <v>81.65</v>
       </c>
-      <c r="Z24" s="33">
+      <c r="Z24" s="35">
         <v>65.68</v>
       </c>
-      <c r="AA24" s="33">
+      <c r="AA24" s="35">
         <v>26.48</v>
       </c>
-      <c r="AB24" s="33">
+      <c r="AB24" s="35">
         <v>30.08</v>
       </c>
-      <c r="AC24" s="33">
+      <c r="AC24" s="35">
         <v>42.18</v>
       </c>
-      <c r="AD24" s="33">
+      <c r="AD24" s="35">
         <v>29.83</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="33" t="s">
         <v>360</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="34">
         <v>1025.9</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="34">
         <v>969.76</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="34">
         <v>785.92</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="34">
         <v>596.27</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="34">
         <v>333.48</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="34">
         <v>194.43</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="34">
         <v>162.01</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="34">
         <v>143.55</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="34">
         <v>115.8</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="34">
         <v>120.16</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="34">
         <v>101.54</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="35">
         <v>88.72</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="35">
         <v>72.93</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="35">
         <v>71.75</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="35">
         <v>62.01</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="35">
         <v>64.21</v>
       </c>
-      <c r="R25" s="33">
+      <c r="R25" s="35">
         <v>76.83</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="35">
         <v>66.78</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="35">
         <v>65.22</v>
       </c>
-      <c r="U25" s="33">
+      <c r="U25" s="35">
         <v>66.83</v>
       </c>
-      <c r="V25" s="33">
+      <c r="V25" s="35">
         <v>69.77</v>
       </c>
-      <c r="W25" s="33">
+      <c r="W25" s="35">
         <v>63.13</v>
       </c>
-      <c r="X25" s="33">
+      <c r="X25" s="35">
         <v>46.5</v>
       </c>
-      <c r="Y25" s="33">
+      <c r="Y25" s="35">
         <v>47.77</v>
       </c>
-      <c r="Z25" s="33">
+      <c r="Z25" s="35">
         <v>39.0</v>
       </c>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="34"/>
-      <c r="AC25" s="34"/>
-      <c r="AD25" s="34"/>
+      <c r="AA25" s="36"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="36"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="33" t="s">
         <v>362</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="34">
         <v>128.85</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="34">
         <v>321.01</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="34">
         <v>385.82</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="34">
         <v>590.68</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="34">
         <v>308.0</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="34">
         <v>104.31</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="35">
         <v>72.82</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="35">
         <v>84.67</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="35">
         <v>56.02</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="35">
         <v>56.16</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="35">
         <v>35.79</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="35">
         <v>32.52</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="35">
         <v>36.99</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="35">
         <v>44.8</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="35">
         <v>26.4</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="35">
         <v>23.55</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="35">
         <v>24.85</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="35">
         <v>30.13</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="35">
         <v>26.32</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="35">
         <v>23.87</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="35">
         <v>26.44</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="35">
         <v>30.22</v>
       </c>
-      <c r="X27" s="33">
+      <c r="X27" s="35">
         <v>20.73</v>
       </c>
-      <c r="Y27" s="33">
+      <c r="Y27" s="35">
         <v>32.66</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="35">
         <v>26.27</v>
       </c>
-      <c r="AA27" s="33">
+      <c r="AA27" s="35">
         <v>21.19</v>
       </c>
-      <c r="AB27" s="33">
+      <c r="AB27" s="35">
         <v>24.07</v>
       </c>
-      <c r="AC27" s="33">
+      <c r="AC27" s="35">
         <v>33.74</v>
       </c>
-      <c r="AD27" s="33">
+      <c r="AD27" s="35">
         <v>23.86</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="33" t="s">
         <v>363</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="34">
         <v>387.96</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="34">
         <v>367.99</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="34">
         <v>300.16</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="34">
         <v>230.16</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="34">
         <v>130.16</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="35">
         <v>75.91</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="35">
         <v>63.27</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="35">
         <v>56.08</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="35">
         <v>45.26</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="35">
         <v>47.12</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="35">
         <v>39.92</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="35">
         <v>34.95</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="35">
         <v>28.8</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="35">
         <v>28.44</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="35">
         <v>24.59</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="35">
         <v>25.53</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="35">
         <v>30.6</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="35">
         <v>26.64</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="35">
         <v>26.07</v>
       </c>
-      <c r="U28" s="33">
+      <c r="U28" s="35">
         <v>26.75</v>
       </c>
-      <c r="V28" s="33">
+      <c r="V28" s="35">
         <v>27.91</v>
       </c>
-      <c r="W28" s="33">
+      <c r="W28" s="35">
         <v>27.46</v>
       </c>
-      <c r="X28" s="33">
+      <c r="X28" s="35">
         <v>22.47</v>
       </c>
-      <c r="Y28" s="33">
+      <c r="Y28" s="35">
         <v>26.62</v>
       </c>
-      <c r="Z28" s="33">
+      <c r="Z28" s="35">
         <v>25.95</v>
       </c>
-      <c r="AA28" s="34"/>
-      <c r="AB28" s="34"/>
-      <c r="AC28" s="34"/>
-      <c r="AD28" s="34"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="36"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="37">
         <v>26.83</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="37">
         <v>9.99</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="37">
         <v>1.83</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="37">
         <v>0.71</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="37">
         <v>11.59</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="37">
         <v>10.99</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="37">
         <v>13.09</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="38">
         <v>-2.67</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="37">
         <v>7.16</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="37">
         <v>5.94</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="37">
         <v>13.58</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="37">
         <v>19.48</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="38">
         <v>-2.57</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="37">
         <v>4.71</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="37">
         <v>9.48</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="37">
         <v>15.21</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="37">
         <v>8.92</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="37">
         <v>7.92</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="37">
         <v>8.91</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="37">
         <v>7.45</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="38">
         <v>-11.96</v>
       </c>
-      <c r="W30" s="35">
+      <c r="W30" s="37">
         <v>11.02</v>
       </c>
-      <c r="X30" s="35">
+      <c r="X30" s="37">
         <v>7.61</v>
       </c>
-      <c r="Y30" s="35">
+      <c r="Y30" s="37">
         <v>0.87</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="37">
         <v>9.07</v>
       </c>
-      <c r="AA30" s="35">
+      <c r="AA30" s="37">
         <v>30.22</v>
       </c>
-      <c r="AB30" s="35"/>
-      <c r="AC30" s="35">
+      <c r="AB30" s="37"/>
+      <c r="AC30" s="37">
         <v>20.84</v>
       </c>
-      <c r="AD30" s="35">
+      <c r="AD30" s="37">
         <v>36.76</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="33" t="s">
         <v>366</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="37">
         <v>6.25</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="37">
         <v>5.19</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="37">
         <v>4.63</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="37">
         <v>4.98</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="37">
         <v>9.25</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="37">
         <v>6.97</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="37">
         <v>6.45</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="37">
         <v>6.52</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="37">
         <v>7.85</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="37">
         <v>7.29</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="37">
         <v>7.98</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="37">
         <v>7.9</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="37">
         <v>5.73</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="37">
         <v>8.46</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="37">
         <v>9.93</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="37">
         <v>9.54</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="37">
         <v>4.14</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="37">
         <v>4.89</v>
       </c>
-      <c r="T31" s="35">
+      <c r="T31" s="37">
         <v>4.65</v>
       </c>
-      <c r="U31" s="35">
+      <c r="U31" s="37">
         <v>2.91</v>
       </c>
-      <c r="V31" s="35">
+      <c r="V31" s="37">
         <v>3.27</v>
       </c>
-      <c r="W31" s="35">
+      <c r="W31" s="37">
         <v>10.58</v>
       </c>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="35"/>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
+      <c r="X31" s="37"/>
+      <c r="Y31" s="37"/>
+      <c r="Z31" s="37"/>
+      <c r="AA31" s="37"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="37"/>
+      <c r="AD31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="31" t="s">
         <v>367</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="33" t="s">
         <v>368</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="37">
         <v>0.0</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="37">
         <v>1.53</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="37">
         <v>1.14</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="37">
         <v>0.68</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="37">
         <v>0.0</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="37">
         <v>3.11</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="37">
         <v>4.35</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="37">
         <v>3.6</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="37">
         <v>4.86</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="37">
         <v>4.27</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="37">
         <v>5.05</v>
       </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35">
+      <c r="M33" s="37"/>
+      <c r="N33" s="37">
         <v>3.97</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="37">
         <v>4.17</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="37">
         <v>3.56</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="37">
         <v>2.83</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="37">
         <v>5.65</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="37">
         <v>5.08</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="37">
         <v>1.51</v>
       </c>
-      <c r="U33" s="35"/>
-      <c r="V33" s="35">
+      <c r="U33" s="37"/>
+      <c r="V33" s="37">
         <v>1.56</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="37">
         <v>6.94</v>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="37">
         <v>10.53</v>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="37">
         <v>7.32</v>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="37">
         <v>15.34</v>
       </c>
-      <c r="AA33" s="35">
+      <c r="AA33" s="37">
         <v>12.81</v>
       </c>
-      <c r="AB33" s="35"/>
-      <c r="AC33" s="35">
+      <c r="AB33" s="37"/>
+      <c r="AC33" s="37">
         <v>9.82</v>
       </c>
-      <c r="AD33" s="35">
+      <c r="AD33" s="37">
         <v>11.96</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="37">
         <v>0.76</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="37">
         <v>0.97</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="37">
         <v>1.03</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="37">
         <v>1.18</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="37">
         <v>2.03</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="37">
         <v>3.91</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="37">
         <v>4.32</v>
       </c>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35">
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37">
         <v>4.01</v>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="37">
         <v>4.24</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="37">
         <v>3.72</v>
       </c>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35">
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37">
         <v>8.19</v>
       </c>
-      <c r="W34" s="35">
+      <c r="W34" s="37">
         <v>10.24</v>
       </c>
-      <c r="X34" s="35"/>
-      <c r="Y34" s="35"/>
-      <c r="Z34" s="35"/>
-      <c r="AA34" s="35"/>
-      <c r="AB34" s="35"/>
-      <c r="AC34" s="35"/>
-      <c r="AD34" s="35"/>
+      <c r="X34" s="37"/>
+      <c r="Y34" s="37"/>
+      <c r="Z34" s="37"/>
+      <c r="AA34" s="37"/>
+      <c r="AB34" s="37"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="33" t="s">
         <v>370</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="37">
         <v>0.0</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="37">
         <v>1.53</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="37">
         <v>1.14</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="37">
         <v>0.68</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="37">
         <v>0.0</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="37">
         <v>3.11</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="37">
         <v>4.35</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="37">
         <v>3.6</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="37">
         <v>4.86</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="37">
         <v>4.27</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="37">
         <v>5.05</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="37">
         <v>5.13</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="37">
         <v>5.95</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="37">
         <v>5.18</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="37">
         <v>4.42</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="37">
         <v>3.52</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="37">
         <v>7.03</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="37">
         <v>6.32</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="37">
         <v>1.88</v>
       </c>
-      <c r="U35" s="35">
+      <c r="U35" s="37">
         <v>1.67</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="37">
         <v>10.59</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="37">
         <v>6.94</v>
       </c>
-      <c r="X35" s="35">
+      <c r="X35" s="37">
         <v>10.53</v>
       </c>
-      <c r="Y35" s="35">
+      <c r="Y35" s="37">
         <v>7.32</v>
       </c>
-      <c r="Z35" s="35">
+      <c r="Z35" s="37">
         <v>15.34</v>
       </c>
-      <c r="AA35" s="35">
+      <c r="AA35" s="37">
         <v>12.81</v>
       </c>
-      <c r="AB35" s="35"/>
-      <c r="AC35" s="35">
+      <c r="AB35" s="37"/>
+      <c r="AC35" s="37">
         <v>0.0</v>
       </c>
-      <c r="AD35" s="35">
+      <c r="AD35" s="37">
         <v>11.96</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="33" t="s">
         <v>371</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="37">
         <v>0.76</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="37">
         <v>0.97</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="37">
         <v>1.03</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="37">
         <v>1.18</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="37">
         <v>2.03</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="37">
         <v>3.91</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="37">
         <v>4.32</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="37">
         <v>4.42</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="37">
         <v>5.02</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="37">
         <v>5.09</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="37">
         <v>5.21</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="37">
         <v>5.01</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="37">
         <v>5.25</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="37">
         <v>5.28</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="37">
         <v>4.62</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="37">
         <v>4.09</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="37">
         <v>5.52</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="37">
         <v>5.6</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="37">
         <v>6.31</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="37">
         <v>7.4</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="37">
         <v>9.9</v>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="37">
         <v>10.24</v>
       </c>
-      <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="35"/>
-      <c r="AA36" s="35"/>
-      <c r="AB36" s="35"/>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
+      <c r="X36" s="37"/>
+      <c r="Y36" s="37"/>
+      <c r="Z36" s="37"/>
+      <c r="AA36" s="37"/>
+      <c r="AB36" s="37"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+      <c r="Z37" s="32"/>
+      <c r="AA37" s="32"/>
+      <c r="AB37" s="32"/>
+      <c r="AC37" s="32"/>
+      <c r="AD37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="33" t="s">
         <v>373</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="35">
         <v>1.54</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="35">
         <v>3.66</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="35">
         <v>4.83</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="35">
         <v>7.19</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="35">
         <v>4.81</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="35">
         <v>1.78</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="35">
         <v>1.43</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="35">
         <v>1.84</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="35">
         <v>1.41</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="35">
         <v>1.55</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="35">
         <v>1.14</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="35">
         <v>1.14</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="35">
         <v>1.45</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="35">
         <v>1.69</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="35">
         <v>1.05</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="35">
         <v>0.95</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="35">
         <v>0.8</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="35">
         <v>1.21</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="35">
         <v>1.06</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="35">
         <v>1.06</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="35">
         <v>1.21</v>
       </c>
-      <c r="W38" s="33">
+      <c r="W38" s="35">
         <v>1.05</v>
       </c>
-      <c r="X38" s="33">
+      <c r="X38" s="35">
         <v>0.79</v>
       </c>
-      <c r="Y38" s="33">
+      <c r="Y38" s="35">
         <v>1.06</v>
       </c>
-      <c r="Z38" s="33">
+      <c r="Z38" s="35">
         <v>0.83</v>
       </c>
-      <c r="AA38" s="33">
+      <c r="AA38" s="35">
         <v>0.38</v>
       </c>
-      <c r="AB38" s="33">
+      <c r="AB38" s="35">
         <v>0.43</v>
       </c>
-      <c r="AC38" s="33">
+      <c r="AC38" s="35">
         <v>0.67</v>
       </c>
-      <c r="AD38" s="33">
+      <c r="AD38" s="35">
         <v>0.55</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="33" t="s">
         <v>374</v>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="35">
         <v>4.47</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="35">
         <v>4.6</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="35">
         <v>4.33</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="35">
         <v>3.82</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="35">
         <v>2.37</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="35">
         <v>1.61</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="35">
         <v>1.49</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="35">
         <v>1.44</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="35">
         <v>1.35</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="35">
         <v>1.4</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="35">
         <v>1.3</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="35">
         <v>1.27</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="35">
         <v>1.2</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="35">
         <v>1.15</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="35">
         <v>1.01</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="35">
         <v>1.01</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="35">
         <v>1.06</v>
       </c>
-      <c r="S39" s="33">
+      <c r="S39" s="35">
         <v>1.12</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="35">
         <v>1.02</v>
       </c>
-      <c r="U39" s="33">
+      <c r="U39" s="35">
         <v>1.02</v>
       </c>
-      <c r="V39" s="33">
+      <c r="V39" s="35">
         <v>0.98</v>
       </c>
-      <c r="W39" s="33">
+      <c r="W39" s="35">
         <v>0.76</v>
       </c>
-      <c r="X39" s="33">
+      <c r="X39" s="35">
         <v>0.63</v>
       </c>
-      <c r="Y39" s="33">
+      <c r="Y39" s="35">
         <v>0.62</v>
       </c>
-      <c r="Z39" s="33">
+      <c r="Z39" s="35">
         <v>0.55</v>
       </c>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
+      <c r="AA39" s="36"/>
+      <c r="AB39" s="36"/>
+      <c r="AC39" s="36"/>
+      <c r="AD39" s="36"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="32"/>
+      <c r="W40" s="32"/>
+      <c r="X40" s="32"/>
+      <c r="Y40" s="32"/>
+      <c r="Z40" s="32"/>
+      <c r="AA40" s="32"/>
+      <c r="AB40" s="32"/>
+      <c r="AC40" s="32"/>
+      <c r="AD40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="33">
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="35">
         <v>1.97</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="35">
         <v>1.6</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="35">
         <v>2.04</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="35">
         <v>1.48</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="35">
         <v>1.59</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="35">
         <v>1.17</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="35">
         <v>1.15</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="35">
         <v>1.45</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="35">
         <v>1.7</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="35">
         <v>1.05</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="35">
         <v>0.95</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="35">
         <v>0.81</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="35">
         <v>1.22</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="35">
         <v>1.08</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="35">
         <v>1.06</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="35">
         <v>1.23</v>
       </c>
-      <c r="W41" s="33">
+      <c r="W41" s="35">
         <v>1.25</v>
       </c>
-      <c r="X41" s="33">
+      <c r="X41" s="35">
         <v>0.96</v>
       </c>
-      <c r="Y41" s="33">
+      <c r="Y41" s="35">
         <v>1.29</v>
       </c>
-      <c r="Z41" s="33">
+      <c r="Z41" s="35">
         <v>0.97</v>
       </c>
-      <c r="AA41" s="33">
+      <c r="AA41" s="35">
         <v>0.45</v>
       </c>
-      <c r="AB41" s="33">
+      <c r="AB41" s="35">
         <v>0.5</v>
       </c>
-      <c r="AC41" s="33">
+      <c r="AC41" s="35">
         <v>0.79</v>
       </c>
-      <c r="AD41" s="33">
+      <c r="AD41" s="35">
         <v>0.64</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="33" t="s">
         <v>377</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="33">
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="35">
         <v>16.43</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="35">
         <v>4.06</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="35">
         <v>1.75</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="35">
         <v>1.59</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="35">
         <v>1.51</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="35">
         <v>1.38</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="35">
         <v>1.41</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="35">
         <v>1.31</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="35">
         <v>1.27</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="35">
         <v>1.21</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="35">
         <v>1.16</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="35">
         <v>1.02</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="35">
         <v>1.02</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="35">
         <v>1.08</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S42" s="35">
         <v>1.17</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="35">
         <v>1.11</v>
       </c>
-      <c r="U42" s="33">
+      <c r="U42" s="35">
         <v>1.16</v>
       </c>
-      <c r="V42" s="33">
+      <c r="V42" s="35">
         <v>1.13</v>
       </c>
-      <c r="W42" s="33">
+      <c r="W42" s="35">
         <v>0.9</v>
       </c>
-      <c r="X42" s="33">
+      <c r="X42" s="35">
         <v>0.75</v>
       </c>
-      <c r="Y42" s="33">
+      <c r="Y42" s="35">
         <v>0.73</v>
       </c>
-      <c r="Z42" s="33">
+      <c r="Z42" s="35">
         <v>0.64</v>
       </c>
-      <c r="AA42" s="34"/>
-      <c r="AB42" s="34"/>
-      <c r="AC42" s="34"/>
-      <c r="AD42" s="34"/>
+      <c r="AA42" s="36"/>
+      <c r="AB42" s="36"/>
+      <c r="AC42" s="36"/>
+      <c r="AD42" s="36"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
+      <c r="W43" s="32"/>
+      <c r="X43" s="32"/>
+      <c r="Y43" s="32"/>
+      <c r="Z43" s="32"/>
+      <c r="AA43" s="32"/>
+      <c r="AB43" s="32"/>
+      <c r="AC43" s="32"/>
+      <c r="AD43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="33" t="s">
         <v>379</v>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="35">
         <v>0.22</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="35">
         <v>0.48</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="35">
         <v>0.61</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="35">
         <v>1.27</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="35">
         <v>0.77</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="35">
         <v>0.45</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="35">
         <v>0.33</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="35">
         <v>0.4</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="35">
         <v>0.39</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="35">
         <v>0.36</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="35">
         <v>0.24</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="35">
         <v>0.24</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="35">
         <v>0.3</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="35">
         <v>0.37</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="35">
         <v>0.26</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="35">
         <v>0.3</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="35">
         <v>0.2</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="35">
         <v>0.31</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="35">
         <v>0.29</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="35">
         <v>0.33</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="35">
         <v>0.35</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="35">
         <v>0.38</v>
       </c>
-      <c r="X44" s="33">
+      <c r="X44" s="35">
         <v>0.3</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="35">
         <v>0.38</v>
       </c>
-      <c r="Z44" s="33">
+      <c r="Z44" s="35">
         <v>0.28</v>
       </c>
-      <c r="AA44" s="33">
+      <c r="AA44" s="35">
         <v>0.14</v>
       </c>
-      <c r="AB44" s="34"/>
-      <c r="AC44" s="33">
+      <c r="AB44" s="36"/>
+      <c r="AC44" s="35">
         <v>0.23</v>
       </c>
-      <c r="AD44" s="33">
+      <c r="AD44" s="35">
         <v>0.22</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="35">
         <v>0.65</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="35">
         <v>0.72</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="35">
         <v>0.75</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="35">
         <v>0.76</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="35">
         <v>0.51</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="35">
         <v>0.39</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="35">
         <v>0.35</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="35">
         <v>0.33</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="35">
         <v>0.31</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="35">
         <v>0.3</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="35">
         <v>0.28</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="35">
         <v>0.29</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="35">
         <v>0.29</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="35">
         <v>0.29</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="35">
         <v>0.27</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="35">
         <v>0.28</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="35">
         <v>0.29</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S45" s="35">
         <v>0.33</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="35">
         <v>0.33</v>
       </c>
-      <c r="U45" s="33">
+      <c r="U45" s="35">
         <v>0.35</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="35">
         <v>0.34</v>
       </c>
-      <c r="W45" s="33">
+      <c r="W45" s="35">
         <v>0.27</v>
       </c>
-      <c r="X45" s="34"/>
-      <c r="Y45" s="34"/>
-      <c r="Z45" s="34"/>
-      <c r="AA45" s="34"/>
-      <c r="AB45" s="34"/>
-      <c r="AC45" s="34"/>
-      <c r="AD45" s="34"/>
+      <c r="X45" s="36"/>
+      <c r="Y45" s="36"/>
+      <c r="Z45" s="36"/>
+      <c r="AA45" s="36"/>
+      <c r="AB45" s="36"/>
+      <c r="AC45" s="36"/>
+      <c r="AD45" s="36"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="31" t="s">
         <v>381</v>
       </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32"/>
+      <c r="AA46" s="32"/>
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
+      <c r="AD46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="33" t="s">
         <v>382</v>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="35">
         <v>3.73</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="35">
         <v>10.01</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="35">
         <v>54.72</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="34">
         <v>140.37</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="35">
         <v>8.63</v>
       </c>
-      <c r="G47" s="33">
+      <c r="G47" s="35">
         <v>9.1</v>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="35">
         <v>7.64</v>
       </c>
-      <c r="I47" s="34"/>
-      <c r="J47" s="33">
+      <c r="I47" s="36"/>
+      <c r="J47" s="35">
         <v>13.96</v>
       </c>
-      <c r="K47" s="33">
+      <c r="K47" s="35">
         <v>16.84</v>
       </c>
-      <c r="L47" s="33">
+      <c r="L47" s="35">
         <v>7.36</v>
       </c>
-      <c r="M47" s="33">
+      <c r="M47" s="35">
         <v>5.13</v>
       </c>
-      <c r="N47" s="34"/>
-      <c r="O47" s="33">
+      <c r="N47" s="36"/>
+      <c r="O47" s="35">
         <v>21.21</v>
       </c>
-      <c r="P47" s="33">
+      <c r="P47" s="35">
         <v>10.55</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="Q47" s="35">
         <v>6.58</v>
       </c>
-      <c r="R47" s="33">
+      <c r="R47" s="35">
         <v>11.21</v>
       </c>
-      <c r="S47" s="33">
+      <c r="S47" s="35">
         <v>12.63</v>
       </c>
-      <c r="T47" s="33">
+      <c r="T47" s="35">
         <v>11.22</v>
       </c>
-      <c r="U47" s="33">
+      <c r="U47" s="35">
         <v>13.43</v>
       </c>
-      <c r="V47" s="34"/>
-      <c r="W47" s="33">
+      <c r="V47" s="36"/>
+      <c r="W47" s="35">
         <v>9.07</v>
       </c>
-      <c r="X47" s="33">
+      <c r="X47" s="35">
         <v>13.15</v>
       </c>
-      <c r="Y47" s="32">
+      <c r="Y47" s="34">
         <v>115.17</v>
       </c>
-      <c r="Z47" s="33">
+      <c r="Z47" s="35">
         <v>11.03</v>
       </c>
-      <c r="AA47" s="33">
+      <c r="AA47" s="35">
         <v>3.31</v>
       </c>
-      <c r="AB47" s="34"/>
-      <c r="AC47" s="33">
+      <c r="AB47" s="36"/>
+      <c r="AC47" s="35">
         <v>4.8</v>
       </c>
-      <c r="AD47" s="33">
+      <c r="AD47" s="35">
         <v>2.72</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="33" t="s">
         <v>383</v>
       </c>
-      <c r="B48" s="33">
+      <c r="B48" s="35">
         <v>16.0</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="35">
         <v>19.28</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="35">
         <v>21.6</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="35">
         <v>20.08</v>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="35">
         <v>10.81</v>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="35">
         <v>14.35</v>
       </c>
-      <c r="H48" s="33">
+      <c r="H48" s="35">
         <v>15.5</v>
       </c>
-      <c r="I48" s="33">
+      <c r="I48" s="35">
         <v>15.33</v>
       </c>
-      <c r="J48" s="33">
+      <c r="J48" s="35">
         <v>12.74</v>
       </c>
-      <c r="K48" s="33">
+      <c r="K48" s="35">
         <v>13.73</v>
       </c>
-      <c r="L48" s="33">
+      <c r="L48" s="35">
         <v>12.53</v>
       </c>
-      <c r="M48" s="33">
+      <c r="M48" s="35">
         <v>12.66</v>
       </c>
-      <c r="N48" s="33">
+      <c r="N48" s="35">
         <v>17.44</v>
       </c>
-      <c r="O48" s="33">
+      <c r="O48" s="35">
         <v>11.82</v>
       </c>
-      <c r="P48" s="33">
+      <c r="P48" s="35">
         <v>10.07</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="35">
         <v>10.48</v>
       </c>
-      <c r="R48" s="33">
+      <c r="R48" s="35">
         <v>24.14</v>
       </c>
-      <c r="S48" s="33">
+      <c r="S48" s="35">
         <v>20.45</v>
       </c>
-      <c r="T48" s="33">
+      <c r="T48" s="35">
         <v>21.49</v>
       </c>
-      <c r="U48" s="33">
+      <c r="U48" s="35">
         <v>34.33</v>
       </c>
-      <c r="V48" s="33">
+      <c r="V48" s="35">
         <v>30.61</v>
       </c>
-      <c r="W48" s="33">
+      <c r="W48" s="35">
         <v>9.45</v>
       </c>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="34"/>
-      <c r="AA48" s="34"/>
-      <c r="AB48" s="34"/>
-      <c r="AC48" s="34"/>
-      <c r="AD48" s="34"/>
+      <c r="X48" s="36"/>
+      <c r="Y48" s="36"/>
+      <c r="Z48" s="36"/>
+      <c r="AA48" s="36"/>
+      <c r="AB48" s="36"/>
+      <c r="AC48" s="36"/>
+      <c r="AD48" s="36"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="32"/>
+      <c r="X49" s="32"/>
+      <c r="Y49" s="32"/>
+      <c r="Z49" s="32"/>
+      <c r="AA49" s="32"/>
+      <c r="AB49" s="32"/>
+      <c r="AC49" s="32"/>
+      <c r="AD49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="33" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="35">
         <v>4.33</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="35">
         <v>9.4</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="35">
         <v>11.45</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="35">
         <v>21.15</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="35">
         <v>15.97</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="35">
         <v>7.4</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="35">
         <v>5.47</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="35">
         <v>8.14</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="35">
         <v>7.24</v>
       </c>
-      <c r="K50" s="33">
+      <c r="K50" s="35">
         <v>6.4</v>
       </c>
-      <c r="L50" s="33">
+      <c r="L50" s="35">
         <v>5.6</v>
       </c>
-      <c r="M50" s="33">
+      <c r="M50" s="35">
         <v>10.26</v>
       </c>
-      <c r="N50" s="33">
+      <c r="N50" s="35">
         <v>10.28</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="35">
         <v>9.24</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="35">
         <v>7.31</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="Q50" s="35">
         <v>41.23</v>
       </c>
-      <c r="R50" s="33">
+      <c r="R50" s="35">
         <v>5.84</v>
       </c>
-      <c r="S50" s="33">
+      <c r="S50" s="35">
         <v>6.96</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="35">
         <v>6.94</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="35">
         <v>9.28</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="35">
         <v>15.2</v>
       </c>
-      <c r="W50" s="33">
+      <c r="W50" s="35">
         <v>11.22</v>
       </c>
-      <c r="X50" s="33">
+      <c r="X50" s="35">
         <v>10.19</v>
       </c>
-      <c r="Y50" s="33">
+      <c r="Y50" s="35">
         <v>6.1</v>
       </c>
-      <c r="Z50" s="33">
+      <c r="Z50" s="35">
         <v>4.4</v>
       </c>
-      <c r="AA50" s="33">
+      <c r="AA50" s="35">
         <v>2.2</v>
       </c>
-      <c r="AB50" s="34"/>
-      <c r="AC50" s="33">
+      <c r="AB50" s="36"/>
+      <c r="AC50" s="35">
         <v>3.47</v>
       </c>
-      <c r="AD50" s="33">
+      <c r="AD50" s="35">
         <v>1.9</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="33" t="s">
         <v>386</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="35">
         <v>12.28</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="35">
         <v>13.34</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="35">
         <v>13.48</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="35">
         <v>13.58</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="35">
         <v>9.52</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="35">
         <v>6.89</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="35">
         <v>6.55</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="35">
         <v>7.28</v>
       </c>
-      <c r="J51" s="33">
+      <c r="J51" s="35">
         <v>7.45</v>
       </c>
-      <c r="K51" s="33">
+      <c r="K51" s="35">
         <v>7.87</v>
       </c>
-      <c r="L51" s="33">
+      <c r="L51" s="35">
         <v>8.27</v>
       </c>
-      <c r="M51" s="33">
+      <c r="M51" s="35">
         <v>10.32</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="35">
         <v>9.39</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="35">
         <v>8.57</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="35">
         <v>7.98</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="Q51" s="35">
         <v>8.38</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="35">
         <v>7.96</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="35">
         <v>9.02</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="35">
         <v>9.94</v>
       </c>
-      <c r="U51" s="33">
+      <c r="U51" s="35">
         <v>9.27</v>
       </c>
-      <c r="V51" s="33">
+      <c r="V51" s="35">
         <v>7.68</v>
       </c>
-      <c r="W51" s="33">
+      <c r="W51" s="35">
         <v>5.13</v>
       </c>
-      <c r="X51" s="34"/>
-      <c r="Y51" s="34"/>
-      <c r="Z51" s="34"/>
-      <c r="AA51" s="34"/>
-      <c r="AB51" s="34"/>
-      <c r="AC51" s="34"/>
-      <c r="AD51" s="34"/>
+      <c r="X51" s="36"/>
+      <c r="Y51" s="36"/>
+      <c r="Z51" s="36"/>
+      <c r="AA51" s="36"/>
+      <c r="AB51" s="36"/>
+      <c r="AC51" s="36"/>
+      <c r="AD51" s="36"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="31" t="s">
         <v>387</v>
       </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
-      <c r="AA52" s="30"/>
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="32"/>
+      <c r="Y52" s="32"/>
+      <c r="Z52" s="32"/>
+      <c r="AA52" s="32"/>
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="33" t="s">
         <v>388</v>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="35">
         <v>29.44</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="35">
         <v>30.84</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="35">
         <v>20.96</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="35">
         <v>42.89</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="35">
         <v>32.64</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="35">
         <v>11.77</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="35">
         <v>7.34</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="35">
         <v>11.98</v>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="35">
         <v>10.96</v>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="35">
         <v>8.15</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="35">
         <v>7.47</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="35">
         <v>17.63</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="35">
         <v>13.21</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="35">
         <v>11.18</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="35">
         <v>9.8</v>
       </c>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="33">
+      <c r="Q53" s="36"/>
+      <c r="R53" s="35">
         <v>9.12</v>
       </c>
-      <c r="S53" s="33">
+      <c r="S53" s="35">
         <v>10.05</v>
       </c>
-      <c r="T53" s="33">
+      <c r="T53" s="35">
         <v>10.8</v>
       </c>
-      <c r="U53" s="33">
+      <c r="U53" s="35">
         <v>21.18</v>
       </c>
-      <c r="V53" s="33">
+      <c r="V53" s="35">
         <v>70.39</v>
       </c>
-      <c r="W53" s="33">
+      <c r="W53" s="35">
         <v>25.94</v>
       </c>
-      <c r="X53" s="33">
+      <c r="X53" s="35">
         <v>30.06</v>
       </c>
-      <c r="Y53" s="33">
+      <c r="Y53" s="35">
         <v>8.41</v>
       </c>
-      <c r="Z53" s="33">
+      <c r="Z53" s="35">
         <v>5.41</v>
       </c>
-      <c r="AA53" s="33">
+      <c r="AA53" s="35">
         <v>3.29</v>
       </c>
-      <c r="AB53" s="34"/>
-      <c r="AC53" s="33">
+      <c r="AB53" s="36"/>
+      <c r="AC53" s="35">
         <v>5.46</v>
       </c>
-      <c r="AD53" s="33">
+      <c r="AD53" s="35">
         <v>2.63</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="33" t="s">
         <v>389</v>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="35">
         <v>30.9</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="35">
         <v>28.05</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="35">
         <v>24.12</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="35">
         <v>23.47</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="35">
         <v>15.21</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="35">
         <v>9.89</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="35">
         <v>9.04</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="35">
         <v>10.36</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="35">
         <v>10.32</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="35">
         <v>10.36</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="35">
         <v>11.06</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="35">
         <v>14.94</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="35">
         <v>13.42</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="35">
         <v>12.6</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="35">
         <v>12.77</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="Q54" s="35">
         <v>14.91</v>
       </c>
-      <c r="R54" s="33">
+      <c r="R54" s="35">
         <v>13.8</v>
       </c>
-      <c r="S54" s="33">
+      <c r="S54" s="35">
         <v>16.8</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="35">
         <v>22.12</v>
       </c>
-      <c r="U54" s="33">
+      <c r="U54" s="35">
         <v>18.45</v>
       </c>
-      <c r="V54" s="33">
+      <c r="V54" s="35">
         <v>12.51</v>
       </c>
-      <c r="W54" s="33">
+      <c r="W54" s="35">
         <v>7.77</v>
       </c>
-      <c r="X54" s="34"/>
-      <c r="Y54" s="34"/>
-      <c r="Z54" s="34"/>
-      <c r="AA54" s="34"/>
-      <c r="AB54" s="34"/>
-      <c r="AC54" s="34"/>
-      <c r="AD54" s="34"/>
+      <c r="X54" s="36"/>
+      <c r="Y54" s="36"/>
+      <c r="Z54" s="36"/>
+      <c r="AA54" s="36"/>
+      <c r="AB54" s="36"/>
+      <c r="AC54" s="36"/>
+      <c r="AD54" s="36"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="30"/>
-      <c r="U55" s="30"/>
-      <c r="V55" s="30"/>
-      <c r="W55" s="30"/>
-      <c r="X55" s="30"/>
-      <c r="Y55" s="30"/>
-      <c r="Z55" s="30"/>
-      <c r="AA55" s="30"/>
-      <c r="AB55" s="30"/>
-      <c r="AC55" s="30"/>
-      <c r="AD55" s="30"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
+      <c r="Z55" s="32"/>
+      <c r="AA55" s="32"/>
+      <c r="AB55" s="32"/>
+      <c r="AC55" s="32"/>
+      <c r="AD55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="33" t="s">
         <v>391</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="35">
         <v>7.96</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="35">
         <v>13.77</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="35">
         <v>14.27</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="35">
         <v>42.89</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="35">
         <v>32.64</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="35">
         <v>11.77</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="35">
         <v>7.34</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="35">
         <v>11.98</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="35">
         <v>10.96</v>
       </c>
-      <c r="K56" s="33">
+      <c r="K56" s="35">
         <v>8.15</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="35">
         <v>7.47</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="35">
         <v>17.63</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="35">
         <v>13.21</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="35">
         <v>11.18</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="35">
         <v>9.8</v>
       </c>
-      <c r="Q56" s="34"/>
-      <c r="R56" s="33">
+      <c r="Q56" s="36"/>
+      <c r="R56" s="35">
         <v>9.12</v>
       </c>
-      <c r="S56" s="33">
+      <c r="S56" s="35">
         <v>10.05</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="35">
         <v>10.82</v>
       </c>
-      <c r="U56" s="33">
+      <c r="U56" s="35">
         <v>21.18</v>
       </c>
-      <c r="V56" s="33">
+      <c r="V56" s="35">
         <v>77.91</v>
       </c>
-      <c r="W56" s="33">
+      <c r="W56" s="35">
         <v>23.81</v>
       </c>
-      <c r="X56" s="33">
+      <c r="X56" s="35">
         <v>30.06</v>
       </c>
-      <c r="Y56" s="33">
+      <c r="Y56" s="35">
         <v>8.41</v>
       </c>
-      <c r="Z56" s="33">
+      <c r="Z56" s="35">
         <v>5.41</v>
       </c>
-      <c r="AA56" s="33">
+      <c r="AA56" s="35">
         <v>3.29</v>
       </c>
-      <c r="AB56" s="34"/>
-      <c r="AC56" s="33">
+      <c r="AB56" s="36"/>
+      <c r="AC56" s="35">
         <v>5.46</v>
       </c>
-      <c r="AD56" s="33">
+      <c r="AD56" s="35">
         <v>6.89</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="33" t="s">
         <v>392</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="35">
         <v>4.47</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="35">
         <v>4.6</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="35">
         <v>4.33</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="35">
         <v>3.82</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="35">
         <v>2.37</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="35">
         <v>1.61</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="35">
         <v>1.49</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="35">
         <v>1.44</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="35">
         <v>1.35</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="35">
         <v>1.4</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="35">
         <v>1.3</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="35">
         <v>1.27</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="35">
         <v>1.2</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="35">
         <v>1.15</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="35">
         <v>1.01</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="35">
         <v>1.01</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="35">
         <v>1.06</v>
       </c>
-      <c r="S57" s="33">
+      <c r="S57" s="35">
         <v>1.15</v>
       </c>
-      <c r="T57" s="33">
+      <c r="T57" s="35">
         <v>1.09</v>
       </c>
-      <c r="U57" s="33">
+      <c r="U57" s="35">
         <v>1.13</v>
       </c>
-      <c r="V57" s="33">
+      <c r="V57" s="35">
         <v>1.11</v>
       </c>
-      <c r="W57" s="33">
+      <c r="W57" s="35">
         <v>0.89</v>
       </c>
-      <c r="X57" s="33">
+      <c r="X57" s="35">
         <v>0.74</v>
       </c>
-      <c r="Y57" s="33">
+      <c r="Y57" s="35">
         <v>0.73</v>
       </c>
-      <c r="Z57" s="33">
+      <c r="Z57" s="35">
         <v>0.64</v>
       </c>
-      <c r="AA57" s="34"/>
-      <c r="AB57" s="34"/>
-      <c r="AC57" s="34"/>
-      <c r="AD57" s="34"/>
+      <c r="AA57" s="36"/>
+      <c r="AB57" s="36"/>
+      <c r="AC57" s="36"/>
+      <c r="AD57" s="36"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
-      <c r="W58" s="30"/>
-      <c r="X58" s="30"/>
-      <c r="Y58" s="30"/>
-      <c r="Z58" s="30"/>
-      <c r="AA58" s="30"/>
-      <c r="AB58" s="30"/>
-      <c r="AC58" s="30"/>
-      <c r="AD58" s="30"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
+      <c r="X58" s="32"/>
+      <c r="Y58" s="32"/>
+      <c r="Z58" s="32"/>
+      <c r="AA58" s="32"/>
+      <c r="AB58" s="32"/>
+      <c r="AC58" s="32"/>
+      <c r="AD58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="33" t="s">
         <v>394</v>
       </c>
-      <c r="B59" s="37">
+      <c r="B59" s="39">
         <v>-0.49</v>
       </c>
-      <c r="C59" s="37">
+      <c r="C59" s="39">
         <v>-0.66</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="35">
         <v>0.76</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="35">
         <v>0.81</v>
       </c>
-      <c r="F59" s="34"/>
-      <c r="G59" s="37">
+      <c r="F59" s="36"/>
+      <c r="G59" s="39">
         <v>-1.17</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="35">
         <v>0.19</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="35">
         <v>0.44</v>
       </c>
-      <c r="J59" s="37">
+      <c r="J59" s="39">
         <v>-0.51</v>
       </c>
-      <c r="K59" s="33">
+      <c r="K59" s="35">
         <v>0.23</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="35">
         <v>0.05</v>
       </c>
-      <c r="M59" s="37">
+      <c r="M59" s="39">
         <v>-0.42</v>
       </c>
-      <c r="N59" s="37">
+      <c r="N59" s="39">
         <v>-0.5</v>
       </c>
-      <c r="O59" s="33">
+      <c r="O59" s="35">
         <v>0.22</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="35">
         <v>0.02</v>
       </c>
-      <c r="Q59" s="34"/>
-      <c r="R59" s="37">
+      <c r="Q59" s="36"/>
+      <c r="R59" s="39">
         <v>-0.35</v>
       </c>
-      <c r="S59" s="33">
+      <c r="S59" s="35">
         <v>0.36</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="35">
         <v>0.1</v>
       </c>
-      <c r="U59" s="33">
+      <c r="U59" s="35">
         <v>0.1</v>
       </c>
-      <c r="V59" s="37">
+      <c r="V59" s="39">
         <v>-1.05</v>
       </c>
-      <c r="W59" s="33">
+      <c r="W59" s="35">
         <v>0.56</v>
       </c>
-      <c r="X59" s="37">
+      <c r="X59" s="39">
         <v>-0.37</v>
       </c>
-      <c r="Y59" s="37">
+      <c r="Y59" s="39">
         <v>-0.49</v>
       </c>
-      <c r="Z59" s="37">
+      <c r="Z59" s="39">
         <v>-0.21</v>
       </c>
-      <c r="AA59" s="34"/>
-      <c r="AB59" s="34"/>
-      <c r="AC59" s="37">
+      <c r="AA59" s="36"/>
+      <c r="AB59" s="36"/>
+      <c r="AC59" s="39">
         <v>-0.15</v>
       </c>
-      <c r="AD59" s="34"/>
+      <c r="AD59" s="36"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="33" t="s">
         <v>395</v>
       </c>
-      <c r="B60" s="37">
+      <c r="B60" s="39">
         <v>-1.91</v>
       </c>
-      <c r="C60" s="37">
+      <c r="C60" s="39">
         <v>-19.11</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="35">
         <v>1.23</v>
       </c>
-      <c r="E60" s="33">
+      <c r="E60" s="35">
         <v>1.2</v>
       </c>
-      <c r="F60" s="33">
+      <c r="F60" s="35">
         <v>3.28</v>
       </c>
-      <c r="G60" s="33">
+      <c r="G60" s="35">
         <v>0.88</v>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="35">
         <v>0.26</v>
       </c>
-      <c r="I60" s="33">
+      <c r="I60" s="35">
         <v>0.77</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="35">
         <v>6.14</v>
       </c>
-      <c r="K60" s="33">
+      <c r="K60" s="35">
         <v>0.66</v>
       </c>
-      <c r="L60" s="34"/>
-      <c r="M60" s="37">
+      <c r="L60" s="36"/>
+      <c r="M60" s="39">
         <v>-3.21</v>
       </c>
-      <c r="N60" s="33">
+      <c r="N60" s="35">
         <v>74.67</v>
       </c>
-      <c r="O60" s="33">
+      <c r="O60" s="35">
         <v>1.07</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="35">
         <v>0.65</v>
       </c>
-      <c r="Q60" s="34"/>
-      <c r="R60" s="33">
+      <c r="Q60" s="36"/>
+      <c r="R60" s="35">
         <v>0.91</v>
       </c>
-      <c r="S60" s="33">
+      <c r="S60" s="35">
         <v>0.53</v>
       </c>
-      <c r="T60" s="37">
+      <c r="T60" s="39">
         <v>-2.33</v>
       </c>
-      <c r="U60" s="37">
+      <c r="U60" s="39">
         <v>-0.74</v>
       </c>
-      <c r="V60" s="37">
+      <c r="V60" s="39">
         <v>-0.29</v>
       </c>
-      <c r="W60" s="34"/>
-      <c r="X60" s="34"/>
-      <c r="Y60" s="34"/>
-      <c r="Z60" s="34"/>
-      <c r="AA60" s="34"/>
-      <c r="AB60" s="34"/>
-      <c r="AC60" s="34"/>
-      <c r="AD60" s="34"/>
+      <c r="W60" s="36"/>
+      <c r="X60" s="36"/>
+      <c r="Y60" s="36"/>
+      <c r="Z60" s="36"/>
+      <c r="AA60" s="36"/>
+      <c r="AB60" s="36"/>
+      <c r="AC60" s="36"/>
+      <c r="AD60" s="36"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
-      <c r="V61" s="30"/>
-      <c r="W61" s="30"/>
-      <c r="X61" s="30"/>
-      <c r="Y61" s="30"/>
-      <c r="Z61" s="30"/>
-      <c r="AA61" s="30"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="30"/>
-      <c r="AD61" s="30"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="32"/>
+      <c r="X61" s="32"/>
+      <c r="Y61" s="32"/>
+      <c r="Z61" s="32"/>
+      <c r="AA61" s="32"/>
+      <c r="AB61" s="32"/>
+      <c r="AC61" s="32"/>
+      <c r="AD61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="B62" s="33">
+      <c r="B62" s="35">
         <v>0.47</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="35">
         <v>0.72</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="35">
         <v>0.82</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="35">
         <v>1.61</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="35">
         <v>0.99</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="35">
         <v>0.4</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="35">
         <v>0.28</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="35">
         <v>0.37</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="35">
         <v>0.28</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="35">
         <v>0.28</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="35">
         <v>0.16</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="35">
         <v>0.17</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="35">
         <v>0.26</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="35">
         <v>0.29</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="35">
         <v>0.18</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="35">
         <v>0.21</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="35">
         <v>0.14</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="35">
         <v>0.26</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="35">
         <v>0.23</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="35">
         <v>0.25</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="35">
         <v>0.34</v>
       </c>
-      <c r="W62" s="33">
+      <c r="W62" s="35">
         <v>0.3</v>
       </c>
-      <c r="X62" s="33">
+      <c r="X62" s="35">
         <v>0.23</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="35">
         <v>0.31</v>
       </c>
-      <c r="Z62" s="33">
+      <c r="Z62" s="35">
         <v>0.22</v>
       </c>
-      <c r="AA62" s="33">
+      <c r="AA62" s="35">
         <v>0.08</v>
       </c>
-      <c r="AB62" s="34"/>
-      <c r="AC62" s="33">
+      <c r="AB62" s="36"/>
+      <c r="AC62" s="35">
         <v>0.19</v>
       </c>
-      <c r="AD62" s="33">
+      <c r="AD62" s="35">
         <v>0.17</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="33" t="s">
         <v>398</v>
       </c>
-      <c r="B63" s="33">
+      <c r="B63" s="35">
         <v>0.89</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="35">
         <v>0.94</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="35">
         <v>0.93</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="35">
         <v>0.9</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="35">
         <v>0.54</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="35">
         <v>0.33</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="35">
         <v>0.28</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="35">
         <v>0.26</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="35">
         <v>0.23</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="35">
         <v>0.23</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="35">
         <v>0.21</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="35">
         <v>0.23</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="35">
         <v>0.22</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="35">
         <v>0.22</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="35">
         <v>0.2</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="35">
         <v>0.22</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="35">
         <v>0.24</v>
       </c>
-      <c r="S63" s="33">
+      <c r="S63" s="35">
         <v>0.27</v>
       </c>
-      <c r="T63" s="33">
+      <c r="T63" s="35">
         <v>0.27</v>
       </c>
-      <c r="U63" s="33">
+      <c r="U63" s="35">
         <v>0.29</v>
       </c>
-      <c r="V63" s="33">
+      <c r="V63" s="35">
         <v>0.28</v>
       </c>
-      <c r="W63" s="33">
+      <c r="W63" s="35">
         <v>0.23</v>
       </c>
-      <c r="X63" s="34"/>
-      <c r="Y63" s="34"/>
-      <c r="Z63" s="34"/>
-      <c r="AA63" s="34"/>
-      <c r="AB63" s="34"/>
-      <c r="AC63" s="34"/>
-      <c r="AD63" s="34"/>
+      <c r="X63" s="36"/>
+      <c r="Y63" s="36"/>
+      <c r="Z63" s="36"/>
+      <c r="AA63" s="36"/>
+      <c r="AB63" s="36"/>
+      <c r="AC63" s="36"/>
+      <c r="AD63" s="36"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="31" t="s">
         <v>399</v>
       </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
-      <c r="S64" s="30"/>
-      <c r="T64" s="30"/>
-      <c r="U64" s="30"/>
-      <c r="V64" s="30"/>
-      <c r="W64" s="30"/>
-      <c r="X64" s="30"/>
-      <c r="Y64" s="30"/>
-      <c r="Z64" s="30"/>
-      <c r="AA64" s="30"/>
-      <c r="AB64" s="30"/>
-      <c r="AC64" s="30"/>
-      <c r="AD64" s="30"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
+      <c r="X64" s="32"/>
+      <c r="Y64" s="32"/>
+      <c r="Z64" s="32"/>
+      <c r="AA64" s="32"/>
+      <c r="AB64" s="32"/>
+      <c r="AC64" s="32"/>
+      <c r="AD64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="33" t="s">
         <v>400</v>
       </c>
-      <c r="B65" s="33">
+      <c r="B65" s="35">
         <v>6.87</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="35">
         <v>10.18</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="35">
         <v>12.63</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="35">
         <v>21.35</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="35">
         <v>15.26</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="35">
         <v>5.31</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="35">
         <v>3.92</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="35">
         <v>6.45</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="35">
         <v>4.11</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="35">
         <v>4.26</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="35">
         <v>3.18</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="35">
         <v>5.79</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="35">
         <v>7.47</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="35">
         <v>6.0</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="35">
         <v>3.97</v>
       </c>
-      <c r="Q65" s="33">
+      <c r="Q65" s="35">
         <v>27.53</v>
       </c>
-      <c r="R65" s="33">
+      <c r="R65" s="35">
         <v>3.5</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="35">
         <v>4.92</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="35">
         <v>4.63</v>
       </c>
-      <c r="U65" s="33">
+      <c r="U65" s="35">
         <v>5.75</v>
       </c>
-      <c r="V65" s="33">
+      <c r="V65" s="35">
         <v>14.29</v>
       </c>
-      <c r="W65" s="33">
+      <c r="W65" s="35">
         <v>8.22</v>
       </c>
-      <c r="X65" s="33">
+      <c r="X65" s="35">
         <v>7.85</v>
       </c>
-      <c r="Y65" s="33">
+      <c r="Y65" s="35">
         <v>4.66</v>
       </c>
-      <c r="Z65" s="33">
+      <c r="Z65" s="35">
         <v>2.33</v>
       </c>
-      <c r="AA65" s="33">
+      <c r="AA65" s="35">
         <v>0.76</v>
       </c>
-      <c r="AB65" s="34"/>
-      <c r="AC65" s="33">
+      <c r="AB65" s="36"/>
+      <c r="AC65" s="35">
         <v>1.68</v>
       </c>
-      <c r="AD65" s="33">
+      <c r="AD65" s="35">
         <v>1.75</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="33" t="s">
         <v>401</v>
       </c>
-      <c r="B66" s="33">
+      <c r="B66" s="35">
         <v>12.98</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="35">
         <v>13.48</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="35">
         <v>13.44</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="35">
         <v>12.95</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="35">
         <v>8.06</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="35">
         <v>4.83</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="35">
         <v>4.45</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="35">
         <v>4.77</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="35">
         <v>4.66</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="35">
         <v>5.1</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="35">
         <v>5.17</v>
       </c>
-      <c r="M66" s="33">
+      <c r="M66" s="35">
         <v>6.45</v>
       </c>
-      <c r="N66" s="33">
+      <c r="N66" s="35">
         <v>5.97</v>
       </c>
-      <c r="O66" s="33">
+      <c r="O66" s="35">
         <v>5.36</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="35">
         <v>4.99</v>
       </c>
-      <c r="Q66" s="33">
+      <c r="Q66" s="35">
         <v>5.4</v>
       </c>
-      <c r="R66" s="33">
+      <c r="R66" s="35">
         <v>5.54</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="35">
         <v>6.46</v>
       </c>
-      <c r="T66" s="33">
+      <c r="T66" s="35">
         <v>7.23</v>
       </c>
-      <c r="U66" s="33">
+      <c r="U66" s="35">
         <v>7.02</v>
       </c>
-      <c r="V66" s="33">
+      <c r="V66" s="35">
         <v>5.31</v>
       </c>
-      <c r="W66" s="33">
+      <c r="W66" s="35">
         <v>3.47</v>
       </c>
-      <c r="X66" s="34"/>
-      <c r="Y66" s="34"/>
-      <c r="Z66" s="34"/>
-      <c r="AA66" s="34"/>
-      <c r="AB66" s="34"/>
-      <c r="AC66" s="34"/>
-      <c r="AD66" s="34"/>
+      <c r="X66" s="36"/>
+      <c r="Y66" s="36"/>
+      <c r="Z66" s="36"/>
+      <c r="AA66" s="36"/>
+      <c r="AB66" s="36"/>
+      <c r="AC66" s="36"/>
+      <c r="AD66" s="36"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
-      <c r="W67" s="30"/>
-      <c r="X67" s="30"/>
-      <c r="Y67" s="30"/>
-      <c r="Z67" s="30"/>
-      <c r="AA67" s="30"/>
-      <c r="AB67" s="30"/>
-      <c r="AC67" s="30"/>
-      <c r="AD67" s="30"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="32"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
+      <c r="W67" s="32"/>
+      <c r="X67" s="32"/>
+      <c r="Y67" s="32"/>
+      <c r="Z67" s="32"/>
+      <c r="AA67" s="32"/>
+      <c r="AB67" s="32"/>
+      <c r="AC67" s="32"/>
+      <c r="AD67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="33" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="35">
         <v>6.44</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="35">
         <v>11.6</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="35">
         <v>35.5</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="35">
         <v>98.21</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="35">
         <v>10.23</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="35">
         <v>7.3</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="35">
         <v>5.35</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="35">
         <v>22.46</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="35">
         <v>6.64</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="35">
         <v>9.7</v>
       </c>
-      <c r="L68" s="33">
+      <c r="L68" s="35">
         <v>3.75</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="35">
         <v>2.56</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="35">
         <v>37.13</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="35">
         <v>13.11</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="35">
         <v>6.73</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="35">
         <v>4.49</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="35">
         <v>6.22</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="35">
         <v>7.65</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="35">
         <v>5.83</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="35">
         <v>6.09</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="35">
         <v>13.86</v>
       </c>
-      <c r="W68" s="33">
+      <c r="W68" s="35">
         <v>5.86</v>
       </c>
-      <c r="X68" s="33">
+      <c r="X68" s="35">
         <v>6.52</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="35">
         <v>13.74</v>
       </c>
-      <c r="Z68" s="33">
+      <c r="Z68" s="35">
         <v>4.71</v>
       </c>
-      <c r="AA68" s="33">
+      <c r="AA68" s="35">
         <v>1.41</v>
       </c>
-      <c r="AB68" s="34"/>
-      <c r="AC68" s="33">
+      <c r="AB68" s="36"/>
+      <c r="AC68" s="35">
         <v>2.26</v>
       </c>
-      <c r="AD68" s="33">
+      <c r="AD68" s="35">
         <v>1.63</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="33" t="s">
         <v>404</v>
       </c>
-      <c r="B69" s="33">
+      <c r="B69" s="35">
         <v>17.31</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="35">
         <v>19.86</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="35">
         <v>21.69</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="35">
         <v>18.98</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="35">
         <v>9.16</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="35">
         <v>8.24</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="35">
         <v>7.68</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="35">
         <v>6.8</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="35">
         <v>6.19</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="35">
         <v>6.96</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="35">
         <v>6.43</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="35">
         <v>6.85</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="35">
         <v>9.8</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="35">
         <v>7.52</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="35">
         <v>6.13</v>
       </c>
-      <c r="Q69" s="33">
+      <c r="Q69" s="35">
         <v>6.02</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="35">
         <v>7.41</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="35">
         <v>7.21</v>
       </c>
-      <c r="T69" s="33">
+      <c r="T69" s="35">
         <v>6.99</v>
       </c>
-      <c r="U69" s="33">
+      <c r="U69" s="35">
         <v>8.31</v>
       </c>
-      <c r="V69" s="33">
+      <c r="V69" s="35">
         <v>7.71</v>
       </c>
-      <c r="W69" s="33">
+      <c r="W69" s="35">
         <v>5.55</v>
       </c>
-      <c r="X69" s="34"/>
-      <c r="Y69" s="34"/>
-      <c r="Z69" s="34"/>
-      <c r="AA69" s="34"/>
-      <c r="AB69" s="34"/>
-      <c r="AC69" s="34"/>
-      <c r="AD69" s="34"/>
+      <c r="X69" s="36"/>
+      <c r="Y69" s="36"/>
+      <c r="Z69" s="36"/>
+      <c r="AA69" s="36"/>
+      <c r="AB69" s="36"/>
+      <c r="AC69" s="36"/>
+      <c r="AD69" s="36"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
-      <c r="P70" s="30"/>
-      <c r="Q70" s="30"/>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
-      <c r="W70" s="30"/>
-      <c r="X70" s="30"/>
-      <c r="Y70" s="30"/>
-      <c r="Z70" s="30"/>
-      <c r="AA70" s="30"/>
-      <c r="AB70" s="30"/>
-      <c r="AC70" s="30"/>
-      <c r="AD70" s="30"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
+      <c r="V70" s="32"/>
+      <c r="W70" s="32"/>
+      <c r="X70" s="32"/>
+      <c r="Y70" s="32"/>
+      <c r="Z70" s="32"/>
+      <c r="AA70" s="32"/>
+      <c r="AB70" s="32"/>
+      <c r="AC70" s="32"/>
+      <c r="AD70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="B71" s="33">
+      <c r="B71" s="35">
         <v>7.91</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71" s="35">
         <v>15.07</v>
       </c>
-      <c r="D71" s="33">
+      <c r="D71" s="35">
         <v>72.97</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="34">
         <v>178.57</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="35">
         <v>11.05</v>
       </c>
-      <c r="G71" s="33">
+      <c r="G71" s="35">
         <v>8.1</v>
       </c>
-      <c r="H71" s="33">
+      <c r="H71" s="35">
         <v>6.52</v>
       </c>
-      <c r="I71" s="34"/>
-      <c r="J71" s="33">
+      <c r="I71" s="36"/>
+      <c r="J71" s="35">
         <v>10.11</v>
       </c>
-      <c r="K71" s="33">
+      <c r="K71" s="35">
         <v>13.06</v>
       </c>
-      <c r="L71" s="33">
+      <c r="L71" s="35">
         <v>4.77</v>
       </c>
-      <c r="M71" s="33">
+      <c r="M71" s="35">
         <v>3.71</v>
       </c>
-      <c r="N71" s="34"/>
-      <c r="O71" s="33">
+      <c r="N71" s="36"/>
+      <c r="O71" s="35">
         <v>16.78</v>
       </c>
-      <c r="P71" s="33">
+      <c r="P71" s="35">
         <v>7.27</v>
       </c>
-      <c r="Q71" s="33">
+      <c r="Q71" s="35">
         <v>4.6</v>
       </c>
-      <c r="R71" s="33">
+      <c r="R71" s="35">
         <v>8.09</v>
       </c>
-      <c r="S71" s="33">
+      <c r="S71" s="35">
         <v>10.45</v>
       </c>
-      <c r="T71" s="33">
+      <c r="T71" s="35">
         <v>9.08</v>
       </c>
-      <c r="U71" s="33">
+      <c r="U71" s="35">
         <v>10.18</v>
       </c>
-      <c r="V71" s="34"/>
-      <c r="W71" s="33">
+      <c r="V71" s="36"/>
+      <c r="W71" s="35">
         <v>7.02</v>
       </c>
-      <c r="X71" s="33">
+      <c r="X71" s="35">
         <v>10.24</v>
       </c>
-      <c r="Y71" s="33">
+      <c r="Y71" s="35">
         <v>96.02</v>
       </c>
-      <c r="Z71" s="33">
+      <c r="Z71" s="35">
         <v>8.68</v>
       </c>
-      <c r="AA71" s="33">
+      <c r="AA71" s="35">
         <v>1.77</v>
       </c>
-      <c r="AB71" s="34"/>
-      <c r="AC71" s="33">
+      <c r="AB71" s="36"/>
+      <c r="AC71" s="35">
         <v>3.8</v>
       </c>
-      <c r="AD71" s="33">
+      <c r="AD71" s="35">
         <v>2.08</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="33" t="s">
         <v>407</v>
       </c>
-      <c r="B72" s="33">
+      <c r="B72" s="35">
         <v>22.15</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="35">
         <v>25.32</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="35">
         <v>27.25</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="35">
         <v>24.09</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="35">
         <v>11.43</v>
       </c>
-      <c r="G72" s="33">
+      <c r="G72" s="35">
         <v>12.13</v>
       </c>
-      <c r="H72" s="33">
+      <c r="H72" s="35">
         <v>12.48</v>
       </c>
-      <c r="I72" s="33">
+      <c r="I72" s="35">
         <v>11.98</v>
       </c>
-      <c r="J72" s="33">
+      <c r="J72" s="35">
         <v>9.63</v>
       </c>
-      <c r="K72" s="33">
+      <c r="K72" s="35">
         <v>10.59</v>
       </c>
-      <c r="L72" s="33">
+      <c r="L72" s="35">
         <v>9.5</v>
       </c>
-      <c r="M72" s="33">
+      <c r="M72" s="35">
         <v>9.78</v>
       </c>
-      <c r="N72" s="33">
+      <c r="N72" s="35">
         <v>13.59</v>
       </c>
-      <c r="O72" s="33">
+      <c r="O72" s="35">
         <v>8.93</v>
       </c>
-      <c r="P72" s="33">
+      <c r="P72" s="35">
         <v>7.59</v>
       </c>
-      <c r="Q72" s="33">
+      <c r="Q72" s="35">
         <v>8.06</v>
       </c>
-      <c r="R72" s="33">
+      <c r="R72" s="35">
         <v>19.75</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="35">
         <v>16.89</v>
       </c>
-      <c r="T72" s="33">
+      <c r="T72" s="35">
         <v>17.59</v>
       </c>
-      <c r="U72" s="33">
+      <c r="U72" s="35">
         <v>28.33</v>
       </c>
-      <c r="V72" s="33">
+      <c r="V72" s="35">
         <v>25.4</v>
       </c>
-      <c r="W72" s="33">
+      <c r="W72" s="35">
         <v>8.72</v>
       </c>
-      <c r="X72" s="34"/>
-      <c r="Y72" s="34"/>
-      <c r="Z72" s="34"/>
-      <c r="AA72" s="34"/>
-      <c r="AB72" s="34"/>
-      <c r="AC72" s="34"/>
-      <c r="AD72" s="34"/>
+      <c r="X72" s="36"/>
+      <c r="Y72" s="36"/>
+      <c r="Z72" s="36"/>
+      <c r="AA72" s="36"/>
+      <c r="AB72" s="36"/>
+      <c r="AC72" s="36"/>
+      <c r="AD72" s="36"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
